--- a/Output/strategy_results_2026-07-28.xlsx
+++ b/Output/strategy_results_2026-07-28.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +29,9 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <sz val="16"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -52,15 +55,33 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,200 +447,234 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ExpiryDate</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>SellStrike</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>BuyStrike</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>SellPremium</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>BuyPremium</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>NetCredit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>MaxProfit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>MaxLoss</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>BreakEven</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>NetDelta</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>NetTheta</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>EstimatedPOP</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>ReturnOnRisk</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Recommendation</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ExpiryDate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Bull Put</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>23550</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" s="3" t="n">
         <v>23250</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" s="3" t="n">
         <v>33.55</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" s="3" t="n">
         <v>16.45</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" s="3" t="n">
         <v>1069.25</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" s="3" t="n">
         <v>18430.75</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" s="3" t="n">
         <v>23533.55</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" s="3" t="n">
         <v>-1.8</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>⭐⭐ Recommended</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Bull Put</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>23600</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" s="3" t="n">
         <v>23300</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" s="3" t="n">
         <v>36.45</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" s="3" t="n">
         <v>19.55</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" s="3" t="n">
         <v>1098.5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" s="3" t="n">
         <v>18401.5</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" s="3" t="n">
         <v>23583.1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" s="3" t="n">
         <v>-0.06</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" s="3" t="n">
         <v>-1.69</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" s="3" t="n">
         <v>5.97</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>⭐⭐ Recommended</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -634,200 +689,234 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ExpiryDate</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>SellStrike</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>BuyStrike</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>SellPremium</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>BuyPremium</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>NetCredit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>MaxProfit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>MaxLoss</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>BreakEven</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>NetDelta</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>NetTheta</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>EstimatedPOP</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>ReturnOnRisk</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Recommendation</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ExpiryDate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Bear Call</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>24950</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" s="3" t="n">
         <v>25250</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" s="3" t="n">
         <v>23.45</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" s="3" t="n">
         <v>17.95</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" s="3" t="n">
         <v>1166.75</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" s="3" t="n">
         <v>18333.25</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" s="3" t="n">
         <v>24967.95</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" s="3" t="n">
         <v>-2.43</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" s="3" t="n">
         <v>6.36</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>⭐⭐ Recommended</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Bear Call</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>24900</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" s="3" t="n">
         <v>25200</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" s="3" t="n">
         <v>30.35</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" s="3" t="n">
         <v>22.95</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" s="3" t="n">
         <v>1491.75</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" s="3" t="n">
         <v>18008.25</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" s="3" t="n">
         <v>24922.95</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" s="3" t="n">
         <v>0.09</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" s="3" t="n">
         <v>-2.74</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" s="3" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>⭐⭐ Recommended</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
         </is>
       </c>
     </row>

--- a/Output/strategy_results_2026-07-28.xlsx
+++ b/Output/strategy_results_2026-07-28.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -611,10 +611,8 @@
       <c r="P2" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>⭐⭐ Recommended</t>
-        </is>
+      <c r="Q2" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -672,10 +670,362 @@
       <c r="P3" s="3" t="n">
         <v>5.97</v>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>⭐⭐ Recommended</t>
-        </is>
+      <c r="Q3" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bull Put</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>23650</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>23350</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1339</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>18161</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>23629.4</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Bull Put</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>23700</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>23400</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>1556.75</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>17943.25</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>23676.05</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bull Put</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>23800</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>23500</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>29.65</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>2063.75</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>17436.25</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>23768.25</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Bull Put</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>23850</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>23550</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>33.55</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>2340</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>17160</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>23814</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bull Put</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>23900</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>23600</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>2551.25</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>16948.75</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>23860.75</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Bull Put</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>24000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>23700</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>99.15000000000001</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>3357.25</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>16142.75</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>23948.35</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -689,7 +1039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -853,10 +1203,8 @@
       <c r="P2" s="3" t="n">
         <v>6.36</v>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>⭐⭐ Recommended</t>
-        </is>
+      <c r="Q2" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -914,10 +1262,185 @@
       <c r="P3" s="3" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>⭐⭐ Recommended</t>
-        </is>
+      <c r="Q3" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bear Call</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>24850</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>25150</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1820</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>17680</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>24878</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Bear Call</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>24800</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>25100</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>2232.75</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>17267.25</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>24834.35</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bear Call</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>24650</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>24950</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>3870.75</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>15629.25</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>24709.55</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
